--- a/GWD Data/Panel Board.xlsx
+++ b/GWD Data/Panel Board.xlsx
@@ -737,7 +737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7674A182-A4E3-4998-9D88-A96BBE96B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F421B14-C93D-4F6B-B012-133E74EAB9A6}">
   <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/GWD Data/Panel Board.xlsx
+++ b/GWD Data/Panel Board.xlsx
@@ -737,7 +737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F421B14-C93D-4F6B-B012-133E74EAB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5E796F0-5B76-4AA5-AA81-BA5A3511B9A6}">
   <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
